--- a/results_polyp/Results_5_ClinicDB_test.xlsx
+++ b/results_polyp/Results_5_ClinicDB_test.xlsx
@@ -472,22 +472,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9595537781715393</v>
+        <v>0.9623579978942871</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9222521781921387</v>
+        <v>0.9274470210075378</v>
       </c>
       <c r="D2" t="n">
-        <v>0.953</v>
+        <v>0.9726</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9953</v>
+        <v>0.9932</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9524</v>
       </c>
       <c r="G2" t="n">
-        <v>3.6056</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -497,22 +497,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9642924666404724</v>
+        <v>0.9612551331520081</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9310470819473267</v>
+        <v>0.9254006147384644</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9859</v>
+        <v>0.9704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9939</v>
+        <v>0.995</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9436</v>
+        <v>0.9522</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7831</v>
+        <v>4.1829</v>
       </c>
     </row>
     <row r="4">
@@ -522,13 +522,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9752199649810791</v>
+        <v>0.9766280055046082</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9516383409500122</v>
+        <v>0.9543235301971436</v>
       </c>
       <c r="D4" t="n">
-        <v>0.98</v>
+        <v>0.983</v>
       </c>
       <c r="E4" t="n">
         <v>0.9982</v>
@@ -537,7 +537,7 @@
         <v>0.9704</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="5">
@@ -547,22 +547,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9693321585655212</v>
+        <v>0.978302001953125</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9404893517494202</v>
+        <v>0.9575256109237671</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9641</v>
+        <v>0.9774</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9981</v>
+        <v>0.9984</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9746</v>
+        <v>0.9792</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6056</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="6">
@@ -572,19 +572,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9852944612503052</v>
+        <v>0.9839597940444946</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9710152149200439</v>
+        <v>0.9684261083602905</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9939</v>
+        <v>0.9942</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9947</v>
+        <v>0.994</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9768</v>
+        <v>0.9739</v>
       </c>
       <c r="G6" t="n">
         <v>2.8284</v>
@@ -597,22 +597,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9636640548706055</v>
+        <v>0.9526766538619995</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9298761487007141</v>
+        <v>0.9096299409866333</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9435</v>
+        <v>0.9478</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9993</v>
+        <v>0.9981</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9847</v>
+        <v>0.9576</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>4.0616</v>
       </c>
     </row>
     <row r="8">
@@ -622,22 +622,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9557521939277649</v>
+        <v>0.9568267464637756</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9152542352676392</v>
+        <v>0.9172270894050598</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9489</v>
+        <v>0.9736</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9994</v>
+        <v>0.999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9627</v>
+        <v>0.9406</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="9">
@@ -647,22 +647,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9682742953300476</v>
+        <v>0.9580804705619812</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9384997487068176</v>
+        <v>0.9195340275764465</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9787</v>
+        <v>0.9761</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9986</v>
+        <v>0.998</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9581</v>
+        <v>0.9407</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -672,19 +672,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9718735814094543</v>
+        <v>0.9698758721351624</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9452860951423645</v>
+        <v>0.9415135979652405</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9697</v>
+        <v>0.9667</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9984</v>
+        <v>0.9983</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9741</v>
+        <v>0.9731</v>
       </c>
       <c r="G10" t="n">
         <v>2.8284</v>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9743735790252686</v>
+        <v>0.9763195514678955</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9500277638435364</v>
+        <v>0.9537346959114075</v>
       </c>
       <c r="D11" t="n">
         <v>0.9865</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9981</v>
+        <v>0.9983</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9625</v>
+        <v>0.9663</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.958711564540863</v>
+        <v>0.9583699703216553</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9206973910331726</v>
+        <v>0.9200675487518311</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9312</v>
+        <v>0.9297</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9996</v>
+        <v>0.9997</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9879</v>
+        <v>0.9888</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1623</v>
+        <v>3.6056</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9593843817710876</v>
+        <v>0.9502394199371338</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9219391942024231</v>
+        <v>0.9051963686943054</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9504</v>
+        <v>0.9665</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9993</v>
+        <v>0.9985000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9685</v>
+        <v>0.9345</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2361</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9791785478591919</v>
+        <v>0.9720898866653442</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9592064023017883</v>
+        <v>0.9456953406333923</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9876</v>
+        <v>0.9832</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9988</v>
+        <v>0.9984</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9709</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9674981236457825</v>
+        <v>0.9677382111549377</v>
       </c>
       <c r="C15" t="n">
-        <v>0.9370424747467041</v>
+        <v>0.9374929666519165</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9765</v>
+        <v>0.9805</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9923</v>
+        <v>0.9917</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9587</v>
+        <v>0.9553</v>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>4.1231</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9321637153625488</v>
+        <v>0.9433924555778503</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8729463219642639</v>
+        <v>0.892850399017334</v>
       </c>
       <c r="D16" t="n">
-        <v>0.969</v>
+        <v>0.9591</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9949</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.898</v>
+        <v>0.9282</v>
       </c>
       <c r="G16" t="n">
-        <v>18.7419</v>
+        <v>16.8212</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9341037273406982</v>
+        <v>0.9575484991073608</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8763551712036133</v>
+        <v>0.9185544848442078</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9832</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9961</v>
+        <v>0.9976</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8897</v>
+        <v>0.9303</v>
       </c>
       <c r="G17" t="n">
-        <v>16.9562</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9614810347557068</v>
+        <v>0.9664229154586792</v>
       </c>
       <c r="C18" t="n">
-        <v>0.925819456577301</v>
+        <v>0.9350274205207825</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9629</v>
+        <v>0.9683</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9988</v>
+        <v>0.9989</v>
       </c>
       <c r="F18" t="n">
-        <v>0.96</v>
+        <v>0.9646</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2361</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9710253477096558</v>
+        <v>0.9642384052276611</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9436824917793274</v>
+        <v>0.9309462904930115</v>
       </c>
       <c r="D19" t="n">
-        <v>0.977</v>
+        <v>0.9897</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9989</v>
+        <v>0.9981</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9651</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>2</v>
+        <v>3.073</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.935300886631012</v>
+        <v>0.9425313472747803</v>
       </c>
       <c r="C20" t="n">
-        <v>0.878464937210083</v>
+        <v>0.8913090229034424</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9137</v>
+        <v>0.9324</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9923</v>
+        <v>0.9911</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9579</v>
+        <v>0.9529</v>
       </c>
       <c r="G20" t="n">
-        <v>19.1832</v>
+        <v>9.316000000000001</v>
       </c>
     </row>
     <row r="21">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9256320595741272</v>
+        <v>0.9599666595458984</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8615596294403076</v>
+        <v>0.923015296459198</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8887</v>
+        <v>0.9465</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9957</v>
+        <v>0.9965000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9657</v>
+        <v>0.9738</v>
       </c>
       <c r="G21" t="n">
-        <v>9.649699999999999</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -972,22 +972,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8408927321434021</v>
+        <v>0.8129429221153259</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7254658341407776</v>
+        <v>0.6848389506340027</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9183</v>
+        <v>0.9119</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.9617</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7755</v>
+        <v>0.7333</v>
       </c>
       <c r="G22" t="n">
-        <v>37.4444</v>
+        <v>61.5796</v>
       </c>
     </row>
     <row r="23">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9537037014961243</v>
+        <v>0.9557064175605774</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9115044474601746</v>
+        <v>0.9151702523231506</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9671</v>
+        <v>0.9913</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9992</v>
+        <v>0.9989</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9406</v>
+        <v>0.9226</v>
       </c>
       <c r="G23" t="n">
         <v>2.2361</v>
@@ -1022,22 +1022,22 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9149926900863647</v>
+        <v>0.9303858280181885</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8433055281639099</v>
+        <v>0.8698331117630005</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9831</v>
+        <v>0.9686</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9946</v>
+        <v>0.9963</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8557</v>
+        <v>0.8951</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -1047,22 +1047,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9509122371673584</v>
+        <v>0.9478065371513367</v>
       </c>
       <c r="C25" t="n">
-        <v>0.9064182043075562</v>
+        <v>0.9007911086082458</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9836</v>
+        <v>0.9465</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9964</v>
+        <v>0.9979</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9203</v>
+        <v>0.9491000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>3.6056</v>
+        <v>4.4721</v>
       </c>
     </row>
     <row r="26">
@@ -1072,22 +1072,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9718838930130005</v>
+        <v>0.9610209465026855</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9453055262565613</v>
+        <v>0.9249666333198547</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9933999999999999</v>
+        <v>0.9939</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9874000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9513</v>
+        <v>0.9302</v>
       </c>
       <c r="G26" t="n">
-        <v>4.1231</v>
+        <v>5.6569</v>
       </c>
     </row>
     <row r="27">
@@ -1097,22 +1097,22 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9698360562324524</v>
+        <v>0.9685863852500916</v>
       </c>
       <c r="C27" t="n">
-        <v>0.9414385557174683</v>
+        <v>0.9390863180160522</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9865</v>
+        <v>0.9872</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9973</v>
+        <v>0.9971</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9537</v>
+        <v>0.9507</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2.8284</v>
       </c>
     </row>
     <row r="28">
@@ -1122,22 +1122,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9561044573783875</v>
+        <v>0.9548166990280151</v>
       </c>
       <c r="C28" t="n">
-        <v>0.9159004688262939</v>
+        <v>0.9135399460792542</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9671999999999999</v>
+        <v>0.9595</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9982</v>
+        <v>0.9984</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9453</v>
+        <v>0.9502</v>
       </c>
       <c r="G28" t="n">
-        <v>2.8284</v>
+        <v>3.1844</v>
       </c>
     </row>
     <row r="29">
@@ -1147,22 +1147,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9463436007499695</v>
+        <v>0.9395676851272583</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8981520533561707</v>
+        <v>0.8860232830047607</v>
       </c>
       <c r="D29" t="n">
-        <v>0.9732</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9961</v>
       </c>
       <c r="F29" t="n">
-        <v>0.921</v>
+        <v>0.9116</v>
       </c>
       <c r="G29" t="n">
-        <v>4.4721</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -1172,22 +1172,22 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9446395039558411</v>
+        <v>0.9365379214286804</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8950870037078857</v>
+        <v>0.8806501030921936</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9449</v>
+        <v>0.9368</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9991</v>
+        <v>0.9989</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9444</v>
+        <v>0.9363</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>3.6056</v>
       </c>
     </row>
     <row r="31">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9291864633560181</v>
+        <v>0.9105305075645447</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8677388429641724</v>
+        <v>0.8357558250427246</v>
       </c>
       <c r="D31" t="n">
-        <v>0.8865</v>
+        <v>0.846</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9992</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9762</v>
+        <v>0.9857</v>
       </c>
       <c r="G31" t="n">
-        <v>8.1516</v>
+        <v>24.1494</v>
       </c>
     </row>
     <row r="32">
@@ -1222,22 +1222,22 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.9265181422233582</v>
+        <v>0.9209476709365845</v>
       </c>
       <c r="C32" t="n">
-        <v>0.863096296787262</v>
+        <v>0.8534782528877258</v>
       </c>
       <c r="D32" t="n">
-        <v>0.8692</v>
+        <v>0.8636</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9992</v>
+        <v>0.9986</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9919</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>28.7804</v>
+        <v>29.7245</v>
       </c>
     </row>
     <row r="33">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.9396652579307556</v>
+        <v>0.9337453842163086</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8861967921257019</v>
+        <v>0.8757246136665344</v>
       </c>
       <c r="D33" t="n">
-        <v>0.9009</v>
+        <v>0.902</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9977</v>
+        <v>0.9959</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9819</v>
+        <v>0.9678</v>
       </c>
       <c r="G33" t="n">
-        <v>23.9152</v>
+        <v>21.9374</v>
       </c>
     </row>
     <row r="34">
@@ -1272,22 +1272,22 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.7273185253143311</v>
+        <v>0.6330618262290955</v>
       </c>
       <c r="C34" t="n">
-        <v>0.571485161781311</v>
+        <v>0.463124006986618</v>
       </c>
       <c r="D34" t="n">
-        <v>0.9724</v>
+        <v>0.969</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9905</v>
+        <v>0.9851</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5809</v>
+        <v>0.4701</v>
       </c>
       <c r="G34" t="n">
-        <v>12.1758</v>
+        <v>228.3462</v>
       </c>
     </row>
     <row r="35">
@@ -1297,22 +1297,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9195583462715149</v>
+        <v>0.9121360182762146</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8510949015617371</v>
+        <v>0.83846515417099</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9308</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9984</v>
+        <v>0.9979</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9086</v>
+        <v>0.8841</v>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>4.2426</v>
       </c>
     </row>
     <row r="36">
@@ -1322,22 +1322,22 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9417573809623718</v>
+        <v>0.8979494571685791</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8899257779121399</v>
+        <v>0.8147988319396973</v>
       </c>
       <c r="D36" t="n">
-        <v>0.9488</v>
+        <v>0.8305</v>
       </c>
       <c r="E36" t="n">
-        <v>0.987</v>
+        <v>0.9962</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9348</v>
+        <v>0.9774</v>
       </c>
       <c r="G36" t="n">
-        <v>17</v>
+        <v>28.0179</v>
       </c>
     </row>
     <row r="37">
@@ -1347,22 +1347,22 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9712082147598267</v>
+        <v>0.9707202911376953</v>
       </c>
       <c r="C37" t="n">
-        <v>0.9440279603004456</v>
+        <v>0.9431064128875732</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9623</v>
+        <v>0.9775</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9985000000000001</v>
+        <v>0.9972</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.9641</v>
       </c>
       <c r="G37" t="n">
-        <v>4.1231</v>
+        <v>3.1623</v>
       </c>
     </row>
     <row r="38">
@@ -1372,22 +1372,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9689857363700867</v>
+        <v>0.9637657999992371</v>
       </c>
       <c r="C38" t="n">
-        <v>0.9398373961448669</v>
+        <v>0.9300656318664551</v>
       </c>
       <c r="D38" t="n">
         <v>0.9495</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9992</v>
+        <v>0.9984</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9893</v>
+        <v>0.9785</v>
       </c>
       <c r="G38" t="n">
-        <v>4.2426</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -1397,13 +1397,13 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.975271463394165</v>
+        <v>0.9741935729980469</v>
       </c>
       <c r="C39" t="n">
-        <v>0.9517363905906677</v>
+        <v>0.9496855139732361</v>
       </c>
       <c r="D39" t="n">
-        <v>0.9681999999999999</v>
+        <v>0.9661</v>
       </c>
       <c r="E39" t="n">
         <v>0.9974</v>
@@ -1412,7 +1412,7 @@
         <v>0.9825</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>5.3852</v>
       </c>
     </row>
     <row r="40">
@@ -1422,22 +1422,22 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7791054844856262</v>
+        <v>0.8854002952575684</v>
       </c>
       <c r="C40" t="n">
-        <v>0.6381431818008423</v>
+        <v>0.794366180896759</v>
       </c>
       <c r="D40" t="n">
-        <v>0.8408</v>
+        <v>0.8312</v>
       </c>
       <c r="E40" t="n">
-        <v>0.992</v>
+        <v>0.9988</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7258</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>77.057</v>
+        <v>9.856400000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1447,22 +1447,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9511455297470093</v>
+        <v>0.9381033778190613</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9068422913551331</v>
+        <v>0.8834224343299866</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9515</v>
+        <v>0.9744</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9972</v>
+        <v>0.9942</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9508</v>
+        <v>0.9044</v>
       </c>
       <c r="G41" t="n">
-        <v>13.3647</v>
+        <v>10.0474</v>
       </c>
     </row>
     <row r="42">
@@ -1472,22 +1472,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9299010038375854</v>
+        <v>0.8960030078887939</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8689859509468079</v>
+        <v>0.8115991950035095</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9592000000000001</v>
+        <v>0.9661</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9977</v>
+        <v>0.9957</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9024</v>
+        <v>0.8354</v>
       </c>
       <c r="G42" t="n">
-        <v>5.8687</v>
+        <v>8.544</v>
       </c>
     </row>
     <row r="43">
@@ -1497,22 +1497,22 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9664613008499146</v>
+        <v>0.9677565097808838</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9350993633270264</v>
+        <v>0.9375272989273071</v>
       </c>
       <c r="D43" t="n">
-        <v>0.9815</v>
+        <v>0.9944</v>
       </c>
       <c r="E43" t="n">
-        <v>0.999</v>
+        <v>0.9988</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9519</v>
+        <v>0.9425</v>
       </c>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="44">
@@ -1522,22 +1522,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9254075288772583</v>
+        <v>0.9531698822975159</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8611706495285034</v>
+        <v>0.9105297327041626</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9196</v>
+        <v>0.9563</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9919</v>
+        <v>0.994</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9313</v>
+        <v>0.95</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
@@ -1547,22 +1547,22 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9595692157745361</v>
+        <v>0.9457675218582153</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9222806692123413</v>
+        <v>0.8971146941184998</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9244</v>
+        <v>0.8978</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9997</v>
+        <v>0.9999</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9976</v>
+        <v>0.9991</v>
       </c>
       <c r="G45" t="n">
-        <v>5.831</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -1572,22 +1572,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9720231890678406</v>
+        <v>0.9617462754249573</v>
       </c>
       <c r="C46" t="n">
-        <v>0.9455692172050476</v>
+        <v>0.9263114333152771</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9497</v>
+        <v>0.9272</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9954</v>
+        <v>0.999</v>
       </c>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>7.2111</v>
       </c>
     </row>
     <row r="47">
@@ -1597,22 +1597,22 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9790696501731873</v>
+        <v>0.9702812433242798</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9589974880218506</v>
+        <v>0.9422779679298401</v>
       </c>
       <c r="D47" t="n">
-        <v>0.9695</v>
+        <v>0.9479</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9979</v>
+        <v>0.9988</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9888</v>
+        <v>0.9937</v>
       </c>
       <c r="G47" t="n">
-        <v>3.6056</v>
+        <v>4.4721</v>
       </c>
     </row>
     <row r="48">
@@ -1622,19 +1622,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.985113799571991</v>
+        <v>0.9872505068778992</v>
       </c>
       <c r="C48" t="n">
-        <v>0.9706642627716064</v>
+        <v>0.9748220443725586</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9767</v>
+        <v>0.9887</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9987</v>
+        <v>0.9971</v>
       </c>
       <c r="F48" t="n">
-        <v>0.9937</v>
+        <v>0.9858</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
@@ -1647,22 +1647,22 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9748655557632446</v>
+        <v>0.9776943325996399</v>
       </c>
       <c r="C49" t="n">
-        <v>0.9509636759757996</v>
+        <v>0.9563620090484619</v>
       </c>
       <c r="D49" t="n">
-        <v>0.9883999999999999</v>
+        <v>0.9745</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9937</v>
+        <v>0.997</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9617</v>
+        <v>0.9809</v>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
@@ -1672,22 +1672,22 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9627020359039307</v>
+        <v>0.9556062817573547</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9280863404273987</v>
+        <v>0.9149866700172424</v>
       </c>
       <c r="D50" t="n">
-        <v>0.9849</v>
+        <v>0.9696</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9954</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9414</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>5.3852</v>
+        <v>6.4031</v>
       </c>
     </row>
     <row r="51">
@@ -1697,22 +1697,22 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9635769128799438</v>
+        <v>0.9654885530471802</v>
       </c>
       <c r="C51" t="n">
-        <v>0.9297139048576355</v>
+        <v>0.9332797527313232</v>
       </c>
       <c r="D51" t="n">
-        <v>0.9867</v>
+        <v>0.9854000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9935</v>
+        <v>0.9941</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9415</v>
+        <v>0.9464</v>
       </c>
       <c r="G51" t="n">
-        <v>5</v>
+        <v>5.8479</v>
       </c>
     </row>
     <row r="52">
@@ -1722,22 +1722,22 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9364039897918701</v>
+        <v>0.9236881732940674</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8804131746292114</v>
+        <v>0.8581975698471069</v>
       </c>
       <c r="D52" t="n">
-        <v>0.9002</v>
+        <v>0.9129</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9984</v>
+        <v>0.9954</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9756</v>
+        <v>0.9347</v>
       </c>
       <c r="G52" t="n">
-        <v>8</v>
+        <v>7.0711</v>
       </c>
     </row>
     <row r="53">
@@ -1747,22 +1747,22 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9311335682868958</v>
+        <v>0.5829954147338867</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8711411952972412</v>
+        <v>0.4114280343055725</v>
       </c>
       <c r="D53" t="n">
-        <v>0.99</v>
+        <v>0.9925</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9943</v>
+        <v>0.9412</v>
       </c>
       <c r="F53" t="n">
-        <v>0.8788</v>
+        <v>0.4127</v>
       </c>
       <c r="G53" t="n">
-        <v>6</v>
+        <v>181.416</v>
       </c>
     </row>
     <row r="54">
@@ -1772,22 +1772,22 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8568137288093567</v>
+        <v>0.6802374720573425</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7494961619377136</v>
+        <v>0.5154241919517517</v>
       </c>
       <c r="D54" t="n">
-        <v>0.8131</v>
+        <v>0.7014</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9963</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>0.9055</v>
+        <v>0.6604</v>
       </c>
       <c r="G54" t="n">
-        <v>29.6968</v>
+        <v>72.0444</v>
       </c>
     </row>
     <row r="55">
@@ -1797,22 +1797,22 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.893401026725769</v>
+        <v>0.922123908996582</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8073394298553467</v>
+        <v>0.8555008172988892</v>
       </c>
       <c r="D55" t="n">
-        <v>0.8245</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9998</v>
+        <v>0.9996</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9748</v>
+        <v>0.9595</v>
       </c>
       <c r="G55" t="n">
-        <v>5.0099</v>
+        <v>2.8284</v>
       </c>
     </row>
     <row r="56">
@@ -1822,22 +1822,22 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9469913840293884</v>
+        <v>0.9429328441619873</v>
       </c>
       <c r="C56" t="n">
-        <v>0.8993197083473206</v>
+        <v>0.8920273184776306</v>
       </c>
       <c r="D56" t="n">
-        <v>0.9253</v>
+        <v>0.9137</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9994</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.9697</v>
+        <v>0.9741</v>
       </c>
       <c r="G56" t="n">
-        <v>2.9571</v>
+        <v>2.8284</v>
       </c>
     </row>
     <row r="57">
@@ -1847,22 +1847,22 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8829194307327271</v>
+        <v>0.8353671431541443</v>
       </c>
       <c r="C57" t="n">
-        <v>0.790381133556366</v>
+        <v>0.7172794342041016</v>
       </c>
       <c r="D57" t="n">
-        <v>0.8901</v>
+        <v>0.9969</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9977</v>
+        <v>0.993</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8758</v>
+        <v>0.7189</v>
       </c>
       <c r="G57" t="n">
-        <v>6</v>
+        <v>10.6862</v>
       </c>
     </row>
     <row r="58">
@@ -1872,22 +1872,22 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.9550316333770752</v>
+        <v>0.8964315056800842</v>
       </c>
       <c r="C58" t="n">
-        <v>0.9139335751533508</v>
+        <v>0.8123025298118591</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9658</v>
+        <v>0.9649</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9976</v>
+        <v>0.992</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9445</v>
+        <v>0.837</v>
       </c>
       <c r="G58" t="n">
-        <v>3.6056</v>
+        <v>16.5529</v>
       </c>
     </row>
     <row r="59">
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9513751268386841</v>
+        <v>0.9441758394241333</v>
       </c>
       <c r="C59" t="n">
-        <v>0.9072597622871399</v>
+        <v>0.8942548036575317</v>
       </c>
       <c r="D59" t="n">
-        <v>0.9861</v>
+        <v>0.9797</v>
       </c>
       <c r="E59" t="n">
-        <v>0.9964</v>
+        <v>0.9961</v>
       </c>
       <c r="F59" t="n">
-        <v>0.919</v>
+        <v>0.9111</v>
       </c>
       <c r="G59" t="n">
         <v>5</v>
@@ -1922,22 +1922,22 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9204373359680176</v>
+        <v>0.8794892430305481</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8526020646095276</v>
+        <v>0.7849003076553345</v>
       </c>
       <c r="D60" t="n">
-        <v>0.9671</v>
+        <v>0.9738</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9965000000000001</v>
+        <v>0.9937</v>
       </c>
       <c r="F60" t="n">
-        <v>0.878</v>
+        <v>0.8018</v>
       </c>
       <c r="G60" t="n">
-        <v>7</v>
+        <v>11.0902</v>
       </c>
     </row>
     <row r="61">
@@ -1947,22 +1947,22 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.9279609322547913</v>
+        <v>0.94782954454422</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8656036257743835</v>
+        <v>0.9008327126502991</v>
       </c>
       <c r="D61" t="n">
-        <v>0.8991</v>
+        <v>0.9385</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9996</v>
+        <v>0.9995000000000001</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9588</v>
+        <v>0.9574</v>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="62">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.9814620614051819</v>
+        <v>0.9753166437149048</v>
       </c>
       <c r="C62" t="n">
-        <v>0.9635988473892212</v>
+        <v>0.9518224596977234</v>
       </c>
       <c r="D62" t="n">
-        <v>0.9741</v>
+        <v>0.9955000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>0.9968</v>
+        <v>0.9866</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9889</v>
+        <v>0.9559</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
@@ -1997,22 +1997,22 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.977935791015625</v>
+        <v>0.970566987991333</v>
       </c>
       <c r="C63" t="n">
-        <v>0.9568242430686951</v>
+        <v>0.9428170323371887</v>
       </c>
       <c r="D63" t="n">
-        <v>0.9665</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.9986</v>
       </c>
       <c r="F63" t="n">
-        <v>0.9896</v>
+        <v>0.9699</v>
       </c>
       <c r="G63" t="n">
-        <v>1.4142</v>
+        <v>2.2361</v>
       </c>
     </row>
     <row r="64">
@@ -2022,22 +2022,22 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.9430918635860566</v>
+        <v>0.9304623286570272</v>
       </c>
       <c r="C64" t="n">
-        <v>0.8954072046664453</v>
+        <v>0.8776356121224742</v>
       </c>
       <c r="D64" t="n">
-        <v>0.949759677419355</v>
+        <v>0.9507096774193547</v>
       </c>
       <c r="E64" t="n">
-        <v>0.996424193548387</v>
+        <v>0.9948354838709678</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9398645161290322</v>
+        <v>0.9198612903225807</v>
       </c>
       <c r="G64" t="n">
-        <v>8.172754838709677</v>
+        <v>14.86969516129032</v>
       </c>
     </row>
   </sheetData>
